--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,13 +500,11 @@
       <c r="F2" t="n">
         <v>48300000000</v>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>15</t>
@@ -545,9 +543,6 @@
       <c r="F3" t="n">
         <v>2000000000</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>15</t>
@@ -586,10 +581,6 @@
       <c r="F4" t="n">
         <v>12099790038</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260713000431</t>
@@ -623,9 +614,6 @@
       <c r="F5" t="n">
         <v>5000000000</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>15</t>
@@ -634,6 +622,244 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260713000370</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>케이엠제약</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>999999765</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260714000515</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>제이스코홀딩스</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>제이스코홀딩스(4,940,711주)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260714000466</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>에이프로젠바이오로직스</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2000000772</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260714000440</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>넥스트칩</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260714000458</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>뉴인텍</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2999999457</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260714000280</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>라피치</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>코넥스</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1999998000</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260714000263</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,10 +652,6 @@
       <c r="F6" t="n">
         <v>999999765</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260714000515</t>
@@ -694,8 +690,6 @@
           <t>제이스코홀딩스(4,940,711주)</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>15</t>
@@ -734,10 +728,6 @@
       <c r="F8" t="n">
         <v>2000000772</v>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260714000440</t>
@@ -771,13 +761,11 @@
       <c r="F9" t="n">
         <v>1500000000</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>15</t>
@@ -816,10 +804,6 @@
       <c r="F10" t="n">
         <v>2999999457</v>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260714000280</t>
@@ -853,13 +837,161 @@
       <c r="F11" t="n">
         <v>1999998000</v>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260714000263</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20260713</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>아이에이</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260713000370</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20260713</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>그래피</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>48300000000</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260713000436</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>20260713</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>에이프로젠</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260713000435</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20260713</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>그래피</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>유상증자(기타주식)</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>12099790038</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260713000431</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -870,10 +870,6 @@
       <c r="F12" t="n">
         <v>5000000000</v>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260713000370</t>
@@ -907,14 +903,11 @@
       <c r="F13" t="n">
         <v>48300000000</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260713000436</t>
@@ -948,10 +941,6 @@
       <c r="F14" t="n">
         <v>2000000000</v>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260713000435</t>
@@ -985,13 +974,46 @@
       <c r="F15" t="n">
         <v>12099790038</v>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260713000431</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20260715</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>에이전트AI</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>3499999440</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260715000175</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1007,13 +1007,231 @@
       <c r="F16" t="n">
         <v>3499999440</v>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260715000175</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20260716</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>우성머티리얼스</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>999997680</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260716000776</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20260716</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>다보링크</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260716000759</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>20260716</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>벡트</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>8350115530</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260716000639</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>20260716</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>베뉴지</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>EB</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>37615500000</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260716000586</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20260716</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>유엑스엔</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>코넥스</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>964818979</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260716000573</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>20260716</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>진영</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>499998897</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260716000400</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1040,10 +1040,6 @@
       <c r="F17" t="n">
         <v>999997680</v>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260716000776</t>
@@ -1077,10 +1073,6 @@
       <c r="F18" t="n">
         <v>3000000000</v>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260716000759</t>
@@ -1114,10 +1106,6 @@
       <c r="F19" t="n">
         <v>8350115530</v>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260716000639</t>
@@ -1151,10 +1139,6 @@
       <c r="F20" t="n">
         <v>37615500000</v>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260716000586</t>
@@ -1188,10 +1172,6 @@
       <c r="F21" t="n">
         <v>964818979</v>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260716000573</t>
@@ -1225,13 +1205,157 @@
       <c r="F22" t="n">
         <v>499998897</v>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260716000400</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20260720</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>졸스</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260720000333</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>20260720</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>제이케이시냅스</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2999999464</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260720000235</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20260720</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>엑시온그룹</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>7999999920</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260720000209</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>20260720</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>주연테크</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260720000194</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,10 +1238,6 @@
       <c r="F23" t="n">
         <v>2000000000</v>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260720000333</t>
@@ -1275,10 +1271,6 @@
       <c r="F24" t="n">
         <v>2999999464</v>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260720000235</t>
@@ -1312,10 +1304,6 @@
       <c r="F25" t="n">
         <v>7999999920</v>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260720000209</t>
@@ -1349,13 +1337,157 @@
       <c r="F26" t="n">
         <v>1000000000</v>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260720000194</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>20260721</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>에코글로우</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260721001320</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>20260721</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>씨엑스아이</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>48000000000</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260721001257</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>20260721</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>에넥스</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260721001251</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20260721</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>딥커머스</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>45170968500</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260721001140</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1370,10 +1370,6 @@
       <c r="F27" t="n">
         <v>500000000</v>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260721001320</t>
@@ -1407,10 +1403,6 @@
       <c r="F28" t="n">
         <v>48000000000</v>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260721001257</t>
@@ -1444,10 +1436,6 @@
       <c r="F29" t="n">
         <v>5000000000</v>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260721001251</t>
@@ -1481,13 +1469,194 @@
       <c r="F30" t="n">
         <v>45170968500</v>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260721001140</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>20260722</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>드림시큐리티</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>25000000000</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260722000529</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>20260722</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>아이티엠반도체</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>20000000000</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260722000510</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>20260722</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SKAI</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260722000475</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>20260722</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>네이처셀</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>17000000000</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260722000378</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>20260722</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>인산가</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1000004720</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260722000262</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1502,10 +1502,6 @@
       <c r="F31" t="n">
         <v>25000000000</v>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260722000529</t>
@@ -1539,10 +1535,6 @@
       <c r="F32" t="n">
         <v>20000000000</v>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260722000510</t>
@@ -1576,10 +1568,6 @@
       <c r="F33" t="n">
         <v>3000000000</v>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260722000475</t>
@@ -1613,10 +1601,6 @@
       <c r="F34" t="n">
         <v>17000000000</v>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260722000378</t>
@@ -1650,13 +1634,120 @@
       <c r="F35" t="n">
         <v>1000004720</v>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260722000262</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>20260723</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>대양금속</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260723000519</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>20260723</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>아리바이오LAB</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1999999749</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260723000448</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>20260723</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>플라즈맵</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>7000001280</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260723000215</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1667,10 +1667,6 @@
       <c r="F36" t="n">
         <v>2000000000</v>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260723000519</t>
@@ -1704,10 +1700,6 @@
       <c r="F37" t="n">
         <v>1999999749</v>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260723000448</t>
@@ -1741,13 +1733,83 @@
       <c r="F38" t="n">
         <v>7000001280</v>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260723000215</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>LS에코에너지</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>30000000000</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260727000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NAVER</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1480899838000</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260727000001</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1766,10 +1766,6 @@
       <c r="F39" t="n">
         <v>30000000000</v>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260727000002</t>
@@ -1803,13 +1799,235 @@
       <c r="F40" t="n">
         <v>1480899838000</v>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260727000001</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20260728</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>엑시온그룹</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2010000000</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260728000486</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>20260728</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>판타지오</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>3499999146</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260728000475</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>20260728</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SK디앤디</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>136723860000</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>NH투자증권</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260728000478</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>20260728</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>플레이그램</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>8499993738</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260728000449</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20260728</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>오에스피</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>2000001294</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260728000333</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>20260728</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한국첨단소재</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260727000408</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1832,10 +1832,6 @@
       <c r="F41" t="n">
         <v>2010000000</v>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260728000486</t>
@@ -1869,10 +1865,6 @@
       <c r="F42" t="n">
         <v>3499999146</v>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260728000475</t>
@@ -1906,9 +1898,6 @@
       <c r="F43" t="n">
         <v>136723860000</v>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>NH투자증권</t>
@@ -1947,10 +1936,6 @@
       <c r="F44" t="n">
         <v>8499993738</v>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260728000449</t>
@@ -1984,10 +1969,6 @@
       <c r="F45" t="n">
         <v>2000001294</v>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260728000333</t>
@@ -2021,13 +2002,120 @@
       <c r="F46" t="n">
         <v>5000000000</v>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260727000408</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>20260729</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>풀무원</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>유상증자(기타주식)</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>39999996388</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260729000514</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>20260729</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>이오플로우</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>25999998000</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260729000238</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>20260729</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>로지스몬</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>코넥스</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>456233440</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260728000501</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2035,10 +2035,6 @@
       <c r="F47" t="n">
         <v>39999996388</v>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260729000514</t>
@@ -2072,10 +2068,6 @@
       <c r="F48" t="n">
         <v>25999998000</v>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260729000238</t>
@@ -2109,13 +2101,46 @@
       <c r="F49" t="n">
         <v>456233440</v>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260728000501</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>20260730</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한주에이알티</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1999996850</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260730000554</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2134,13 +2134,194 @@
       <c r="F50" t="n">
         <v>1999996850</v>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260730000554</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>8700600000</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260803000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>KG모빌리티</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>108142500000</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260803000001</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260731000816</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260731000813</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>2203340048</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260731000812</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2167,10 +2167,6 @@
       <c r="F51" t="n">
         <v>8700600000</v>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260803000002</t>
@@ -2204,10 +2200,6 @@
       <c r="F52" t="n">
         <v>108142500000</v>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260803000001</t>
@@ -2241,10 +2233,6 @@
       <c r="F53" t="n">
         <v>10000000000</v>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260731000816</t>
@@ -2278,10 +2266,6 @@
       <c r="F54" t="n">
         <v>10000000000</v>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260731000813</t>
@@ -2315,13 +2299,83 @@
       <c r="F55" t="n">
         <v>2203340048</v>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260731000812</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>하나머티리얼즈</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>EB</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>100000000000</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260804000510</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>유엑스엔</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>코넥스</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>유상증자(기타주식)</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>5000002200</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260804000354</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2332,10 +2332,6 @@
       <c r="F56" t="n">
         <v>100000000000</v>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260804000510</t>
@@ -2369,13 +2365,161 @@
       <c r="F57" t="n">
         <v>5000002200</v>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260804000354</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>20260805</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>30000000000</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260805000480</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>20260805</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>APS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260805000477</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>20260805</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>우리기술</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>40000000000</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260805000463</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>20260805</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>진원생명과학</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>14999999060</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>진원생명(18,176,581주)</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260804000549</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2398,10 +2398,6 @@
       <c r="F58" t="n">
         <v>30000000000</v>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260805000480</t>
@@ -2435,10 +2431,6 @@
       <c r="F59" t="n">
         <v>10000000000</v>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260805000477</t>
@@ -2472,10 +2464,6 @@
       <c r="F60" t="n">
         <v>40000000000</v>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260805000463</t>
@@ -2514,12 +2502,120 @@
           <t>진원생명(18,176,581주)</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260804000549</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>에이프로젠</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>50000000000</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260810000727</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>에이프로젠</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260810000708</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>엠엑스로보틱스</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>9999997920</v>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260807000794</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2535,10 +2535,6 @@
       <c r="F62" t="n">
         <v>50000000000</v>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260810000727</t>
@@ -2572,10 +2568,6 @@
       <c r="F63" t="n">
         <v>2000000000</v>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260810000708</t>
@@ -2609,13 +2601,83 @@
       <c r="F64" t="n">
         <v>9999997920</v>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260807000794</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>20260812</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>덴티스</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>8000000000</v>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260812000755</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>20260812</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>대동금속</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>8997000000</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260812000426</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2634,10 +2634,6 @@
       <c r="F65" t="n">
         <v>8000000000</v>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260812000755</t>
@@ -2671,13 +2667,46 @@
       <c r="F66" t="n">
         <v>8997000000</v>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260812000426</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>20260813</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>엔시트론</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>5999999136</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260813001235</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2700,13 +2700,239 @@
       <c r="F67" t="n">
         <v>5999999136</v>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260813001235</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>엑시온그룹</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>2789200000</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260818000280</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>한국첨단소재</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>2999999310</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260818000277</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>아이에이</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>10267500000</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>에스케이증권</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260818000250</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>이오플로우</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>신종자본증권(333,333주)</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260818000256</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>케스피온</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>12999999792</v>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260818000149</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>유상증자(기타주식)</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>299999970000</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260818000126</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2733,10 +2733,6 @@
       <c r="F68" t="n">
         <v>2789200000</v>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260818000280</t>
@@ -2770,10 +2766,6 @@
       <c r="F69" t="n">
         <v>2999999310</v>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260818000277</t>
@@ -2807,9 +2799,6 @@
       <c r="F70" t="n">
         <v>10267500000</v>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>에스케이증권</t>
@@ -2853,9 +2842,6 @@
           <t>신종자본증권(333,333주)</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260818000256</t>
@@ -2889,10 +2875,6 @@
       <c r="F72" t="n">
         <v>12999999792</v>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260818000149</t>
@@ -2926,13 +2908,83 @@
       <c r="F73" t="n">
         <v>299999970000</v>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260818000126</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>20260819</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>KX하이텍</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>11000000000</v>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260819000309</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>20260819</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>헝셩그룹</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>5248059000</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260819000182</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2941,10 +2941,6 @@
       <c r="F74" t="n">
         <v>11000000000</v>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260819000309</t>
@@ -2978,13 +2974,366 @@
       <c r="F75" t="n">
         <v>5248059000</v>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260819000182</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>넥사다이내믹스</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>8000000000</v>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000329</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>넥사다이내믹스</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>13000000713</v>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000324</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>32500000000</v>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000337</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>62500000000</v>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000304</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>67500000000</v>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000325</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>오르비텍</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000272</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>37500000000</v>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000269</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>그리드위즈</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000168</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>그리드위즈</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>15000000000</v>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000164</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3007,10 +3007,6 @@
       <c r="F76" t="n">
         <v>8000000000</v>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000329</t>
@@ -3044,10 +3040,6 @@
       <c r="F77" t="n">
         <v>13000000713</v>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000324</t>
@@ -3081,14 +3073,11 @@
       <c r="F78" t="n">
         <v>32500000000</v>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000337</t>
@@ -3122,14 +3111,11 @@
       <c r="F79" t="n">
         <v>62500000000</v>
       </c>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000304</t>
@@ -3163,14 +3149,11 @@
       <c r="F80" t="n">
         <v>67500000000</v>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000325</t>
@@ -3204,10 +3187,6 @@
       <c r="F81" t="n">
         <v>5000000000</v>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000272</t>
@@ -3241,14 +3220,11 @@
       <c r="F82" t="n">
         <v>37500000000</v>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000269</t>
@@ -3282,14 +3258,11 @@
       <c r="F83" t="n">
         <v>10000000000</v>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000168</t>
@@ -3323,17 +3296,203 @@
       <c r="F84" t="n">
         <v>15000000000</v>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260824000164</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>20260826</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>삼성FN리츠</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>97090000000</v>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>삼성증권</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260826000684</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>20260826</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>에코글로우</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>4999999312</v>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260826000647</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>20260826</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>육일씨엔에쓰</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>2999999376</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260826000436</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>20260826</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>육일씨엔에쓰</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>2999999318</v>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260826000431</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>20260826</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>씨피시스템</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260826000286</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3334,9 +3334,6 @@
       <c r="F85" t="n">
         <v>97090000000</v>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>삼성증권</t>
@@ -3375,10 +3372,6 @@
       <c r="F86" t="n">
         <v>4999999312</v>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260826000647</t>
@@ -3412,10 +3405,6 @@
       <c r="F87" t="n">
         <v>2999999376</v>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260826000436</t>
@@ -3449,10 +3438,6 @@
       <c r="F88" t="n">
         <v>2999999318</v>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260826000431</t>
@@ -3486,13 +3471,198 @@
       <c r="F89" t="n">
         <v>10000000000</v>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260826000286</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>20260827</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>진코스텍</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>코넥스</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>16644764960</v>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>하나증권</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260827001026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>20260827</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>태영건설</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>50503666290</v>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260827000833</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>20260827</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>더코디</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>499997795</v>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260827000846</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>20260827</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>KG모빌리티</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>154500000000</v>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260827000861</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>20260827</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>더코디</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1499999255</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260827000813</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3504,9 +3504,6 @@
       <c r="F90" t="n">
         <v>16644764960</v>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>하나증권</t>
@@ -3545,10 +3542,6 @@
       <c r="F91" t="n">
         <v>50503666290</v>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260827000833</t>
@@ -3582,10 +3575,6 @@
       <c r="F92" t="n">
         <v>499997795</v>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260827000846</t>
@@ -3619,10 +3608,6 @@
       <c r="F93" t="n">
         <v>154500000000</v>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260827000861</t>
@@ -3656,13 +3641,120 @@
       <c r="F94" t="n">
         <v>1499999255</v>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260827000813</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>20260831</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>신테카바이오</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1999999090</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260831001532</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>20260831</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>파이온엑스</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>9999999315</v>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260831001458</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>20260831</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>아이티센씨티에스</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260831001414</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3674,10 +3674,6 @@
       <c r="F95" t="n">
         <v>1999999090</v>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260831001532</t>
@@ -3711,10 +3707,6 @@
       <c r="F96" t="n">
         <v>9999999315</v>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260831001458</t>
@@ -3748,13 +3740,194 @@
       <c r="F97" t="n">
         <v>5000000000</v>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260831001414</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>로지스몬</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>코넥스</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>466213601</v>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260901000339</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>신화프리텍</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>21000000000</v>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260901000319</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>핀텔</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>2999999520</v>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260901000293</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>엑시온그룹</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1874500000</v>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260901000241</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>성호전자</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>13000000000</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260831001545</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3773,10 +3773,6 @@
       <c r="F98" t="n">
         <v>466213601</v>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260901000339</t>
@@ -3810,10 +3806,6 @@
       <c r="F99" t="n">
         <v>21000000000</v>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260901000319</t>
@@ -3847,10 +3839,6 @@
       <c r="F100" t="n">
         <v>2999999520</v>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260901000293</t>
@@ -3884,10 +3872,6 @@
       <c r="F101" t="n">
         <v>1874500000</v>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260901000241</t>
@@ -3921,13 +3905,157 @@
       <c r="F102" t="n">
         <v>13000000000</v>
       </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260831001545</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>한국첨단소재</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>9700000000</v>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260902000259</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>한국첨단소재</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260902000256</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>볼빅</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>코넥스</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>유상증자(기타주식)</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>9999994215</v>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260902000253</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>삼성제약</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>6000000000</v>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260902000227</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3938,10 +3938,6 @@
       <c r="F103" t="n">
         <v>9700000000</v>
       </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260902000259</t>
@@ -3975,10 +3971,6 @@
       <c r="F104" t="n">
         <v>5000000000</v>
       </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260902000256</t>
@@ -4012,10 +4004,6 @@
       <c r="F105" t="n">
         <v>9999994215</v>
       </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260902000253</t>
@@ -4049,13 +4037,161 @@
       <c r="F106" t="n">
         <v>6000000000</v>
       </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260902000227</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>20260903</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>비케이홀딩스</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>4270000000</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>비케이홀딩스(23,534,735주)</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260903000395</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>20260903</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>에이프로젠바이오로직스</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>20000001094</v>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260903000316</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>20260903</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>에이프로젠</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>20000000000</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260903000285</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>20260903</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>파이온엑스</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>2299998987</v>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260903000148</t>
         </is>
       </c>
     </row>
